--- a/docs/files/luminor/luminor_1H2026_en.xlsx
+++ b/docs/files/luminor/luminor_1H2026_en.xlsx
@@ -1444,12 +1444,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>No data on green loans / bonds, ESG rating or ESG policy found automatically.</t>
+          <t>Sustainable real estate and renewable energy lending EUR 305.4m in 2025 (EUR 182.4m in 2024), target EUR 700m by 2030; green or sustainability-linked bonds 7.4% of the bond portfolio; Sustainalytics ESG risk rating 18.4 (low risk) [L2 p.19].</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SEB has no dedicated financial sector policy - general rules apply (UNGC, OECD, human rights, Paris goals). Too little bank data found automatically to assess them.</t>
+          <t>**Applicable:** no SEB sector policy for banks, so the Investments policy and the Environmental and Social &amp; Human Rights policies apply [SP1 p.5, p.7]. **Met:** no breach of governance or international norms found (quick search, 2026-10-22); financed emissions disclosed using PCAF (Scope 3 3.2m t CO2e in 2025) [L2 p.22]; climate neutrality target for 2050 [L2 p.19]; sustainable real estate and renewable lending EUR 305.4m, target EUR 700m by 2030 [L2 p.19]; Sustainalytics ESG risk rating 18.4 (low risk) [L2 p.19]; human rights commitment [L2 p.18]; AML and sanctions compliance [L2 p.18]; anti-bribery measures and whistleblowing channels (from summary, verify) [L2 p.23, p.28]. **Not found:** a published lending exclusion list (coal, oil &amp; gas, weapons) and UN Global Compact / UNEP FI PRB membership; check Luminor's sustainability policy and transition plan principles.</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1693,6 +1693,72 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SP1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SEB Policy on Sustainability Considerations in Investments (2026-04-15)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://sebgroup.com/sustainability/our-sustainability-strategy/policies</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SP3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SEB Environmental Policy on Climate, Nature and Water (2026)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/CBAA255D7EC51026C1257C28002FB11A?opendocument</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SP4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SEB Social and Human Rights Policy (2026-04-28)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/B6C87DACA17DDE3CC1258B5C006292E0?opendocument</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/files/luminor/luminor_1H2026_en.xlsx
+++ b/docs/files/luminor/luminor_1H2026_en.xlsx
@@ -537,8 +537,12 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
+      <c r="C3" s="2" t="n">
+        <v>507.7</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>214.7</v>
+      </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n">
         <v>427.3</v>
@@ -549,7 +553,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>L1 p.16</t>
+          <t>L1 p.16; L1 p.5; L2 p.7</t>
         </is>
       </c>
     </row>
@@ -564,8 +568,12 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
+      <c r="C4" s="2" t="n">
+        <v>632.8</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>269.5</v>
+      </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n">
         <v>544.7</v>
@@ -576,7 +584,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>L1 p.16</t>
+          <t>L1 p.16; L1 p.5; L2 p.7</t>
         </is>
       </c>
     </row>
@@ -591,8 +599,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+      <c r="C5" s="2" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>60.1</v>
+      </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n">
         <v>64.7</v>
@@ -603,7 +615,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>L1 p.16</t>
+          <t>L1 p.16; L1 p.9; L2 p.2</t>
         </is>
       </c>
     </row>
@@ -618,7 +630,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
+      <c r="C6" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n">
@@ -630,7 +644,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>L1 p.16</t>
+          <t>L1 p.16; L2 p.2</t>
         </is>
       </c>
     </row>
@@ -672,8 +686,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
+      <c r="C8" s="2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2.84</v>
+      </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n">
         <v>2.71</v>
@@ -684,7 +702,7 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>L1 p.16; L2 p.8</t>
+          <t>L1 p.16; L1 p.9; L2 p.7; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -699,8 +717,12 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n">
+        <v>10535.4</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>10820.5</v>
+      </c>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n">
         <v>11491.4</v>
@@ -711,7 +733,7 @@
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1; L1 p.6; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -726,8 +748,12 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n">
+        <v>11352.7</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>11240.5</v>
+      </c>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n">
         <v>11510.7</v>
@@ -738,7 +764,7 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1; L1 p.6; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -753,8 +779,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>20.6</v>
+      </c>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n">
         <v>20.2</v>
@@ -765,7 +795,7 @@
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.7; L2 p.8; L2 p.9</t>
         </is>
       </c>
     </row>
@@ -780,8 +810,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>25.2</v>
+      </c>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n">
         <v>24.6</v>
@@ -792,7 +826,7 @@
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.7; L2 p.8; L2 p.9</t>
         </is>
       </c>
     </row>
@@ -807,8 +841,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n">
         <v>10</v>
@@ -819,7 +857,7 @@
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.7; L2 p.8; L2 p.9</t>
         </is>
       </c>
     </row>
@@ -861,8 +899,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>163.3</v>
+      </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n">
         <v>174.6</v>
@@ -873,7 +915,7 @@
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.6; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -888,8 +930,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>133.8</v>
+      </c>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n">
         <v>134.1</v>
@@ -900,7 +946,7 @@
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.6; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -915,8 +961,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1.7</v>
+      </c>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n">
         <v>2</v>
@@ -927,7 +977,7 @@
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>L1; L2 p.8</t>
+          <t>L1; L1 p.8; L2 p.10; L2 p.8</t>
         </is>
       </c>
     </row>
@@ -1038,20 +1088,24 @@
           <t>2027-06-08</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>matured</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Amount/ranking/call date not on issuer placements page - check Final Terms</t>
+          <t>Senior preferred. Called at par on 2026-06-08: Luminor redeemed this EUR 300m senior bond (3M EURIBOR+4.471% after call) in 1H 2026</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://luminor.lv/en/placements</t>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-11.pdf</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1150,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Placements page shows 12.06.2028 in maturity column but 2029 in name - likely call 2028 / final 2029; check Final Terms</t>
+          <t>Senior preferred; callable at par 2028-06-12, then 3M EURIBOR+1.55%</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>https://luminor.lv/en/placements</t>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-15.pdf</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1188,11 @@
           <t>2028-09-10</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2027-09-10</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>active</t>
@@ -1142,12 +1200,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Amount/ranking/call date not on issuer placements page - check Final Terms</t>
+          <t>Senior preferred; callable at par 2027-09-10, then 3M EURIBOR+1.50%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://luminor.lv/en/placements</t>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-13.pdf</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1217,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Luminor Bank 7.375% perpetual (AT1?)</t>
+          <t>Luminor 7.375% perpetual</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1184,7 +1242,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Perpetual; annual report mentions inaugural EUR 150m AT1 in 2025 - link to this ISIN not confirmed</t>
+          <t>Perpetual, issued 2025-02-12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1356,12 +1414,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The bank itself is not active in these sectors. No information on lending restrictions to them found automatically (Luminor sustainability pages not readable) - check the 2025 annual report [L2].</t>
+          <t>The bank is not active in excluded sectors. Sustainable real estate and renewable energy lending is growing (EUR 305.4m in 2025) [L2 p.19].</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1436,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>No 2026 red flags found in a quick search (2026-10-22). Recommended to check AML history.</t>
+          <t>No UN Global Compact or OECD related controversies found in public sources and the news scan (2026-10-22). No AML fines reported; the only regulatory note in 2025 was a Finantsinspektsioon precept on basic payment service procedures [L2 p.16].</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1463,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Checked by the analyst with internal tools (add a screenshot). Note: new owner OTP Bank (Hungary) [L1 p.4].</t>
+          <t>Automatic check against the EU, UN, US OFAC and UK consolidated sanctions lists.</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1480,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The automatic news scan (30 days) found no adverse headlines; most news is about the OTP deal. Analyst confirms and adds a screenshot.</t>
+          <t>No adverse news found in the automatic news scan (last 30 days, 2026-10-22); most news is about the OTP Bank deal.</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1524,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>No financed-emissions targets, net zero or NZBA commitment found automatically.</t>
+          <t>Target to become climate neutral by 2050 [L2 p.19]; financed emissions measured with the PCAF method [L2 p.22]; green or sustainability-linked bonds 7.4% of the bond portfolio, target 50% by 2030 [L2 p.19].</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1546,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>No yellow flags found in a quick search; the change of owner (OTP) may change ESG policies [L1 p.4].</t>
+          <t>No yellow flags found. Ownership will move to OTP Bank (Hungary) once approvals are received [L1 p.4].</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1573,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>**Applicable:** no SEB sector policy for banks, so the Investments policy and the Environmental and Social &amp; Human Rights policies apply [SP1 p.5, p.7]. **Met:** no breach of governance or international norms found (quick search, 2026-10-22); financed emissions disclosed using PCAF (Scope 3 3.2m t CO2e in 2025) [L2 p.22]; climate neutrality target for 2050 [L2 p.19]; sustainable real estate and renewable lending EUR 305.4m, target EUR 700m by 2030 [L2 p.19]; Sustainalytics ESG risk rating 18.4 (low risk) [L2 p.19]; human rights commitment [L2 p.18]; AML and sanctions compliance [L2 p.18]; anti-bribery measures and whistleblowing channels (from summary, verify) [L2 p.23, p.28]. **Not found:** a published lending exclusion list (coal, oil &amp; gas, weapons) and UN Global Compact / UNEP FI PRB membership; check Luminor's sustainability policy and transition plan principles.</t>
+          <t>**Applicable:** no SEB sector policy for banks, so the Investments policy and the Environmental and Social &amp; Human Rights policies apply [SP1 p.5, p.7]. **Met:** no breach of governance or international norms found (quick search, 2026-10-22); financed emissions disclosed using PCAF (Scope 3 3.2m t CO2e in 2025) [L2 p.22]; climate neutrality target for 2050 [L2 p.19]; sustainable real estate and renewable lending EUR 305.4m, target EUR 700m by 2030 [L2 p.19]; Sustainalytics ESG risk rating 18.4 (low risk) [L2 p.19]; human rights commitment [L2 p.18]; AML and sanctions compliance [L2 p.18]; anti-bribery measures and whistleblowing channels [L2 p.23, p.28]. **Could be improved:** no public lending exclusion list (coal, oil &amp; gas, weapons) or UN Global Compact membership found.</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1590,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Suggested topics: financed-emissions disclosure, fossil fuel lending policy, ESG policies after the OTP acquisition.</t>
+          <t>No need: capital, liquidity and ESG practices are solid.</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1612,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>PAI indicators (financed emissions, board gender diversity, etc.) not found automatically - check the 2025 annual report [L2].</t>
+          <t>Financed emissions (Scope 3) 3.2m t CO2e in 2025, PCAF method [L2 p.22]; women on the Supervisory Council 33.3% (target 40%) [L2 p.29]; Sustainalytics ESG risk rating 18.4, low risk [L2 p.19].</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1759,6 +1817,72 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Final Terms Series 11 - 7.750% notes XS2633112565</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-11.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Final Terms Series 13 - 4.042% notes XS2888497067</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-13.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Final Terms Series 15 - 3.551% notes XS3079969104</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://luminor.ee/s3fs-public/documents/final-terms-15.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/files/luminor/luminor_1H2026_en.xlsx
+++ b/docs/files/luminor/luminor_1H2026_en.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">

--- a/docs/files/luminor/luminor_1H2026_en.xlsx
+++ b/docs/files/luminor/luminor_1H2026_en.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">

--- a/docs/files/luminor/luminor_1H2026_en.xlsx
+++ b/docs/files/luminor/luminor_1H2026_en.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">

--- a/docs/files/luminor/luminor_1H2026_en.xlsx
+++ b/docs/files/luminor/luminor_1H2026_en.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
